--- a/backend/src/db/demo-docs/measurements-flex-sports-bra.xlsx
+++ b/backend/src/db/demo-docs/measurements-flex-sports-bra.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Poly Spandex Blend</t>
+          <t>88% Polyester 12% Spandex</t>
         </is>
       </c>
     </row>
@@ -685,19 +685,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E13" s="5" t="n">
         <v>23.5</v>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="F13" s="5" t="n">
         <v>24.5</v>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="G13" s="5" t="n">
         <v>25.5</v>
       </c>
-      <c r="G13" s="5" t="n">
+      <c r="H13" s="5" t="n">
         <v>26.5</v>
       </c>
     </row>
@@ -778,19 +781,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D16" s="5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="E16" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="E16" s="5" t="n">
+      <c r="F16" s="5" t="n">
         <v>15.5</v>
       </c>
-      <c r="F16" s="5" t="n">
+      <c r="G16" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="G16" s="5" t="n">
+      <c r="H16" s="5" t="n">
         <v>16.5</v>
       </c>
     </row>
@@ -903,19 +909,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="E20" s="5" t="n">
         <v>37.5</v>
       </c>
-      <c r="E20" s="5" t="n">
+      <c r="F20" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="F20" s="5" t="n">
+      <c r="G20" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="G20" s="5" t="n">
+      <c r="H20" s="5" t="n">
         <v>41</v>
       </c>
     </row>
@@ -964,19 +973,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="E22" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="E22" s="5" t="n">
+      <c r="F22" s="5" t="n">
         <v>35.5</v>
       </c>
-      <c r="F22" s="5" t="n">
+      <c r="G22" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="G22" s="5" t="n">
+      <c r="H22" s="5" t="n">
         <v>39</v>
       </c>
     </row>
